--- a/ITTKI_Nazorat/docs/samples/istisnolar.xlsx
+++ b/ITTKI_Nazorat/docs/samples/istisnolar.xlsx
@@ -508,7 +508,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Tuzilgan: 11.10.2026 16:41 · ITTKI Nazorat</t>
+          <t>Tuzilgan: 12.10.2026 05:41 · ITTKI Nazorat</t>
         </is>
       </c>
     </row>
@@ -781,7 +781,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Raxmatullayev S.N., Ichki auditor / Audit qo'mitasi, 11.10.2026</t>
+          <t>Raxmatullayev S.N., Ichki auditor / Audit qo'mitasi, 12.10.2026</t>
         </is>
       </c>
     </row>

--- a/ITTKI_Nazorat/docs/samples/istisnolar.xlsx
+++ b/ITTKI_Nazorat/docs/samples/istisnolar.xlsx
@@ -508,7 +508,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Tuzilgan: 12.10.2026 05:41 · ITTKI Nazorat</t>
+          <t>Tuzilgan: 11.10.2026 10:00:30 (Toshkent, UTC+5) · ITTKI Nazorat</t>
         </is>
       </c>
     </row>
@@ -781,7 +781,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Raxmatullayev S.N., Ichki auditor / Audit qo'mitasi, 12.10.2026</t>
+          <t>Raxmatullayev S.N., Ichki auditor / Audit qo'mitasi, 11.10.2026</t>
         </is>
       </c>
     </row>
